--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -1,46 +1,209 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="comunas" sheetId="1" r:id="rId1"/>
+    <sheet name="Comunas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$B$34</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chépica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chimbarongo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coltauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doñihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graneros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Estrella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litueche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lolol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostazal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paredones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peralillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peumo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichidegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichilemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pumanque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta de Tilcoco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rengo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requínoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fernando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 19:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comunal_e_mat_a_2018_o_higgins.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasa de matrícula población de 0 a 24 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins (Comunal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,21 +211,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -112,10 +291,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -141,15 +316,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -175,6 +347,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,353 +523,360 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Comuna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chépica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>73.72263</v>
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>73.72</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Chimbarongo</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>72.40297</v>
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>72.4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Codegua</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>73.91208</v>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>73.91</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Coinco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>73.76581</v>
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>73.77</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Coltauco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>71.47698</v>
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>71.48</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Doñihue</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>74.19476</v>
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>74.19</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Graneros</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>72.37675</v>
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>72.38</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>La Estrella</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>76.33674999999999</v>
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>76.34</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Las Cabras</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>72.51837</v>
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>72.52</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Litueche</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>70.4461</v>
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>70.45</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Lolol</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>74.75915000000001</v>
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>74.76</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Machalí</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>75.1311</v>
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>75.13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Malloa</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>69.92583</v>
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>69.93</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Marchihue</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>71.3278</v>
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>71.33</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Mostazal</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>73.22393</v>
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>73.22</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Nancagua</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>72.88249</v>
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>72.88</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Navidad</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>70.67973000000001</v>
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>70.68</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Olivar</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>73.59299</v>
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>73.59</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Palmilla</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>72.56953</v>
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>72.57</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Paredones</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>69.47311000000001</v>
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>69.47</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Peralillo</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>74.67672</v>
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>74.68</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Peumo</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>73.22868</v>
+      <c r="A23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>73.23</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pichidegua</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>71.80826</v>
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>71.81</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Pichilemu</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>69.31099</v>
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>69.31</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Placilla</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>70.09125</v>
+      <c r="A26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>70.09</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Pumanque</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>71.0779</v>
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>71.08</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Quinta de Tilcoco</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>73.82013000000001</v>
+      <c r="A28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>73.82</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Rancagua</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>72.85418</v>
+      <c r="A29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>72.85</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Rengo</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>73.20184</v>
+      <c r="A30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>73.2</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Requínoa</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>72.65542000000001</v>
+      <c r="A31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>72.66</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>San Fernando</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>74.77370000000001</v>
+      <c r="A32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>74.77</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>74.8656</v>
+      <c r="A33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>74.87</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>73.36417</v>
+      <c r="A34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>73.36</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B34"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:38</t>
+    <t xml:space="preserve">2026-08-02 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:39</t>
+    <t xml:space="preserve">2026-08-05 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:31</t>
+    <t xml:space="preserve">2026-08-05 18:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:12</t>
+    <t xml:space="preserve">2026-08-16 09:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:43</t>
+    <t xml:space="preserve">2026-08-19 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:38</t>
+    <t xml:space="preserve">2026-08-28 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_o_higgins.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:20</t>
+    <t xml:space="preserve">2026-09-06 17:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
